--- a/tools/importer/reports/import-wknd-homepage.report.xlsx
+++ b/tools/importer/reports/import-wknd-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>wknd-homepage</t>
   </si>
   <si>
-    <t>2026-08-05T07:43:57.941Z</t>
+    <t>2026-08-06T08:48:14.425Z</t>
   </si>
   <si>
     <t>WKND Adventures and Travel</t>
